--- a/data/Branch Plan 2025.xlsx
+++ b/data/Branch Plan 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\mapa lucru\ATK_db\Import_Excel_in_db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE5B9B4-46F5-484B-8413-8B4185C67099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C0B97C-4CBF-44CE-84F4-451699341087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27705" yWindow="2865" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="2250" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Product_Segment</t>
-  </si>
-  <si>
-    <t>Produs_Ajustat</t>
   </si>
   <si>
     <t>BranchRegion</t>
@@ -211,6 +208,9 @@
   </si>
   <si>
     <t>Retail Creditare</t>
+  </si>
+  <si>
+    <t>Produs_Adjusted</t>
   </si>
 </sst>
 </file>
@@ -606,42 +606,42 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
         <v>45930</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="2">
         <v>5912500</v>
@@ -655,22 +655,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
         <v>45930</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
       </c>
       <c r="G3" s="2">
         <v>9250000</v>
@@ -684,22 +684,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1">
         <v>45930</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -713,22 +713,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1">
         <v>45930</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2">
         <v>4362500</v>
@@ -742,22 +742,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
         <v>45930</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2">
         <v>8400000</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>45930</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
       </c>
       <c r="G7" s="2">
         <v>5000000</v>
@@ -800,22 +800,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1">
         <v>45930</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="2">
         <v>7125000</v>
@@ -829,22 +829,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1">
         <v>45930</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2">
         <v>8000000</v>
@@ -858,22 +858,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1">
         <v>45930</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2">
         <v>7000000</v>
@@ -887,22 +887,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1">
         <v>45930</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="2">
         <v>15562500</v>
@@ -916,22 +916,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1">
         <v>45930</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
       </c>
       <c r="G12" s="2">
         <v>64131250</v>
@@ -945,22 +945,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1">
         <v>45930</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="3">
         <v>50800000</v>
@@ -974,22 +974,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
         <v>45930</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" t="s">
         <v>11</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="2">
         <v>4562500</v>
@@ -1003,22 +1003,22 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1">
         <v>45930</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" s="2">
         <v>5700000</v>
@@ -1032,22 +1032,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1">
         <v>45930</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G16" s="2">
         <v>54587500</v>
@@ -1061,22 +1061,22 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1">
         <v>45930</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2">
         <v>30562500</v>
@@ -1090,22 +1090,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1">
         <v>45961</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
       </c>
       <c r="G18" s="2">
         <v>5010000</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1">
         <v>45961</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
         <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
       </c>
       <c r="G19" s="2">
         <v>6875000</v>
@@ -1148,22 +1148,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1">
         <v>45961</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -1177,22 +1177,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1">
         <v>45961</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" s="2">
         <v>2635000</v>
@@ -1206,22 +1206,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>45961</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" s="2">
         <v>7500000</v>
@@ -1235,22 +1235,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
         <v>45961</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
         <v>24</v>
-      </c>
-      <c r="F23" t="s">
-        <v>25</v>
       </c>
       <c r="G23" s="2">
         <v>4000000</v>
@@ -1264,22 +1264,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1">
         <v>45961</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" s="2">
         <v>7670000</v>
@@ -1293,22 +1293,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1">
         <v>45961</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" s="2">
         <v>8000000</v>
@@ -1322,22 +1322,22 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1">
         <v>45961</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="2">
         <v>6000000</v>
@@ -1351,22 +1351,22 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1">
         <v>45961</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G27" s="2">
         <v>13235000</v>
@@ -1380,22 +1380,22 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1">
         <v>45961</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" t="s">
         <v>35</v>
-      </c>
-      <c r="F28" t="s">
-        <v>36</v>
       </c>
       <c r="G28" s="2">
         <v>50065000</v>
@@ -1409,22 +1409,22 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1">
         <v>45961</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G29" s="2">
         <v>41130000</v>
@@ -1438,22 +1438,22 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1">
         <v>45961</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G30" s="2">
         <v>3735000</v>
@@ -1467,22 +1467,22 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1">
         <v>45961</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" s="2">
         <v>4750000</v>
@@ -1496,22 +1496,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="1">
         <v>45961</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G32" s="2">
         <v>43360000</v>
@@ -1525,22 +1525,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
         <v>45961</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="2">
         <v>32285000</v>
@@ -1554,22 +1554,22 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" s="1">
         <v>45991</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" t="s">
         <v>11</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
       </c>
       <c r="G34" s="2">
         <v>5010000</v>
@@ -1583,22 +1583,22 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="1">
         <v>45991</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
         <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>16</v>
       </c>
       <c r="G35" s="2">
         <v>9675000</v>
@@ -1612,22 +1612,22 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" s="1">
         <v>45991</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -1641,22 +1641,22 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1">
         <v>45991</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="2">
         <v>3135000</v>
@@ -1670,22 +1670,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="1">
         <v>45991</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" s="2">
         <v>8500000</v>
@@ -1699,22 +1699,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" s="1">
         <v>45991</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
         <v>24</v>
-      </c>
-      <c r="F39" t="s">
-        <v>25</v>
       </c>
       <c r="G39" s="2">
         <v>5200000</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" s="1">
         <v>45991</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G40" s="2">
         <v>7670000</v>
@@ -1757,22 +1757,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" s="1">
         <v>45991</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G41" s="2">
         <v>11000000</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="1">
         <v>45991</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G42" s="2">
         <v>8000000</v>
@@ -1815,22 +1815,22 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" s="1">
         <v>45991</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" t="s">
         <v>11</v>
       </c>
-      <c r="E43" t="s">
-        <v>12</v>
-      </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G43" s="2">
         <v>13235000</v>
@@ -1844,22 +1844,22 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" s="1">
         <v>45991</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
         <v>35</v>
-      </c>
-      <c r="F44" t="s">
-        <v>36</v>
       </c>
       <c r="G44" s="2">
         <v>50065000</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1">
         <v>45991</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G45" s="2">
         <v>41130000</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1">
         <v>45991</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" t="s">
         <v>11</v>
       </c>
-      <c r="E46" t="s">
-        <v>12</v>
-      </c>
       <c r="F46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" s="2">
         <v>3635000</v>
@@ -1931,22 +1931,22 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="1">
         <v>45991</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" t="s">
         <v>11</v>
       </c>
-      <c r="E47" t="s">
-        <v>12</v>
-      </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G47" s="2">
         <v>4750000</v>
@@ -1960,22 +1960,22 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="1">
         <v>45991</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G48" s="2">
         <v>43360000</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B49" s="1">
         <v>45991</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="2">
         <v>27385000</v>
@@ -2018,22 +2018,22 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="1">
         <v>46022</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" t="s">
         <v>11</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
       </c>
       <c r="G50" s="2">
         <v>6412500</v>
@@ -2047,22 +2047,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" s="1">
         <v>46022</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
         <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
       </c>
       <c r="G51" s="2">
         <v>13250000</v>
@@ -2076,22 +2076,22 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" s="1">
         <v>46022</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="1">
         <v>46022</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G53" s="2">
         <v>4862500</v>
@@ -2134,22 +2134,22 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B54" s="1">
         <v>46022</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" t="s">
         <v>11</v>
       </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
       <c r="F54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G54" s="2">
         <v>10900000</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B55" s="1">
         <v>46022</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" t="s">
         <v>24</v>
-      </c>
-      <c r="F55" t="s">
-        <v>25</v>
       </c>
       <c r="G55" s="2">
         <v>7600000</v>
@@ -2192,22 +2192,22 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B56" s="1">
         <v>46022</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G56" s="2">
         <v>10025000</v>
@@ -2221,22 +2221,22 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B57" s="1">
         <v>46022</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G57" s="2">
         <v>15300000</v>
@@ -2250,22 +2250,22 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="1">
         <v>46022</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" s="2">
         <v>11400000</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59" s="1">
         <v>46022</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" t="s">
         <v>11</v>
       </c>
-      <c r="E59" t="s">
-        <v>12</v>
-      </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G59" s="2">
         <v>15562500</v>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" s="1">
         <v>46022</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E60" t="s">
+        <v>34</v>
+      </c>
+      <c r="F60" t="s">
         <v>35</v>
-      </c>
-      <c r="F60" t="s">
-        <v>36</v>
       </c>
       <c r="G60" s="2">
         <v>68387500</v>
@@ -2337,22 +2337,22 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" s="1">
         <v>46022</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G61" s="2">
         <v>57850000</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" s="1">
         <v>46022</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" t="s">
         <v>11</v>
       </c>
-      <c r="E62" t="s">
-        <v>12</v>
-      </c>
       <c r="F62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G62" s="2">
         <v>4062500</v>
@@ -2395,22 +2395,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" s="1">
         <v>46022</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" t="s">
         <v>11</v>
       </c>
-      <c r="E63" t="s">
-        <v>12</v>
-      </c>
       <c r="F63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G63" s="2">
         <v>6700000</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64" s="1">
         <v>46022</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G64" s="2">
         <v>60600000</v>
@@ -2453,22 +2453,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="1">
         <v>46022</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2">
         <v>32562500</v>
@@ -2482,22 +2482,22 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" s="1">
         <v>45930</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2">
         <v>1306764</v>
@@ -2511,22 +2511,22 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B67" s="1">
         <v>45930</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G67" s="2">
         <v>542200</v>
@@ -2540,22 +2540,22 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B68" s="1">
         <v>45930</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G68" s="2">
         <v>431300</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" s="1">
         <v>45930</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
         <v>15</v>
-      </c>
-      <c r="F69" t="s">
-        <v>16</v>
       </c>
       <c r="G69" s="2">
         <v>578400</v>
@@ -2598,22 +2598,22 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" s="1">
         <v>45930</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G70" s="2">
         <v>396847</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B71" s="1">
         <v>45930</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G71" s="2">
         <v>765469</v>
@@ -2656,22 +2656,22 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B72" s="1">
         <v>45930</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G72" s="2">
         <v>708100</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" s="1">
         <v>45930</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" t="s">
         <v>24</v>
-      </c>
-      <c r="F73" t="s">
-        <v>25</v>
       </c>
       <c r="G73" s="2">
         <v>362075</v>
@@ -2714,22 +2714,22 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B74" s="1">
         <v>45930</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G74" s="2">
         <v>1814160</v>
@@ -2743,22 +2743,22 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B75" s="1">
         <v>45930</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G75" s="2">
         <v>1212755</v>
@@ -2772,22 +2772,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" s="1">
         <v>45930</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" t="s">
         <v>35</v>
-      </c>
-      <c r="F76" t="s">
-        <v>36</v>
       </c>
       <c r="G76" s="2">
         <v>1663272</v>
@@ -2801,22 +2801,22 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" s="1">
         <v>45930</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G77" s="2">
         <v>937235</v>
@@ -2830,22 +2830,22 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" s="1">
         <v>45930</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G78" s="2">
         <v>405500</v>
@@ -2859,22 +2859,22 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B79" s="1">
         <v>45930</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G79" s="2">
         <v>692100</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B80" s="1">
         <v>45930</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G80" s="2">
         <v>540200</v>
@@ -2917,22 +2917,22 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B81" s="1">
         <v>45930</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" t="s">
         <v>12</v>
-      </c>
-      <c r="F81" t="s">
-        <v>13</v>
       </c>
       <c r="G81" s="2">
         <v>772350</v>
@@ -2946,22 +2946,22 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B82" s="1">
         <v>45961</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G82" s="2">
         <v>1187212</v>
@@ -2975,22 +2975,22 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B83" s="1">
         <v>45961</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G83" s="2">
         <v>436100</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B84" s="1">
         <v>45961</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G84" s="2">
         <v>576500</v>
@@ -3033,22 +3033,22 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B85" s="1">
         <v>45961</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
         <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>16</v>
       </c>
       <c r="G85" s="2">
         <v>201800</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B86" s="1">
         <v>45961</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G86" s="2">
         <v>255900</v>
@@ -3091,22 +3091,22 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B87" s="1">
         <v>45961</v>
       </c>
       <c r="C87" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G87" s="2">
         <v>677300</v>
@@ -3120,22 +3120,22 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" s="1">
         <v>45961</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G88" s="2">
         <v>542642</v>
@@ -3149,22 +3149,22 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B89" s="1">
         <v>45961</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E89" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89" t="s">
         <v>24</v>
-      </c>
-      <c r="F89" t="s">
-        <v>25</v>
       </c>
       <c r="G89" s="2">
         <v>309900</v>
@@ -3178,22 +3178,22 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B90" s="1">
         <v>45961</v>
       </c>
       <c r="C90" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G90" s="2">
         <v>1544880</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B91" s="1">
         <v>45961</v>
       </c>
       <c r="C91" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F91" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G91" s="2">
         <v>1609278</v>
@@ -3236,22 +3236,22 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" s="1">
         <v>45961</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E92" t="s">
+        <v>34</v>
+      </c>
+      <c r="F92" t="s">
         <v>35</v>
-      </c>
-      <c r="F92" t="s">
-        <v>36</v>
       </c>
       <c r="G92" s="2">
         <v>1411705</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B93" s="1">
         <v>45961</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G93" s="2">
         <v>848002</v>
@@ -3294,22 +3294,22 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B94" s="1">
         <v>45961</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G94" s="2">
         <v>362200</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" s="1">
         <v>45961</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G95" s="2">
         <v>727766</v>
@@ -3352,22 +3352,22 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" s="1">
         <v>45961</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G96" s="2">
         <v>441654</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B97" s="1">
         <v>45961</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" t="s">
         <v>12</v>
-      </c>
-      <c r="F97" t="s">
-        <v>13</v>
       </c>
       <c r="G97" s="2">
         <v>605900</v>
@@ -3410,22 +3410,22 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B98" s="1">
         <v>45991</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G98" s="2">
         <v>908460</v>
@@ -3439,22 +3439,22 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B99" s="1">
         <v>45991</v>
       </c>
       <c r="C99" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G99" s="2">
         <v>258135</v>
@@ -3468,22 +3468,22 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B100" s="1">
         <v>45991</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G100" s="2">
         <v>528068</v>
@@ -3497,22 +3497,22 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101" s="1">
         <v>45991</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E101" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" t="s">
         <v>15</v>
-      </c>
-      <c r="F101" t="s">
-        <v>16</v>
       </c>
       <c r="G101" s="2">
         <v>69500</v>
@@ -3526,22 +3526,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B102" s="1">
         <v>45991</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G102" s="2">
         <v>240625</v>
@@ -3555,22 +3555,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" s="1">
         <v>45991</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G103" s="2">
         <v>391460</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B104" s="1">
         <v>45991</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F104" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G104" s="2">
         <v>323000</v>
@@ -3613,22 +3613,22 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B105" s="1">
         <v>45991</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E105" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105" t="s">
         <v>24</v>
-      </c>
-      <c r="F105" t="s">
-        <v>25</v>
       </c>
       <c r="G105" s="2">
         <v>350000</v>
@@ -3642,22 +3642,22 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B106" s="1">
         <v>45991</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G106" s="2">
         <v>1405005.5999999999</v>
@@ -3671,22 +3671,22 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B107" s="1">
         <v>45991</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F107" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G107" s="2">
         <v>1085350</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" s="1">
         <v>45991</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E108" t="s">
+        <v>34</v>
+      </c>
+      <c r="F108" t="s">
         <v>35</v>
-      </c>
-      <c r="F108" t="s">
-        <v>36</v>
       </c>
       <c r="G108" s="2">
         <v>890329</v>
@@ -3729,22 +3729,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B109" s="1">
         <v>45991</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F109" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G109" s="2">
         <v>507000</v>
@@ -3758,22 +3758,22 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B110" s="1">
         <v>45991</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G110" s="2">
         <v>311400</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B111" s="1">
         <v>45991</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G111" s="2">
         <v>389500</v>
@@ -3816,22 +3816,22 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B112" s="1">
         <v>45991</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G112" s="2">
         <v>291000</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B113" s="1">
         <v>45991</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
         <v>12</v>
-      </c>
-      <c r="F113" t="s">
-        <v>13</v>
       </c>
       <c r="G113" s="2">
         <v>256500</v>
@@ -3874,22 +3874,22 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B114" s="1">
         <v>46022</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G114" s="2">
         <v>2432959</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B115" s="1">
         <v>46022</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G115" s="2">
         <v>676800</v>
@@ -3932,22 +3932,22 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B116" s="1">
         <v>46022</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G116" s="2">
         <v>846200</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B117" s="1">
         <v>46022</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E117" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" t="s">
         <v>15</v>
-      </c>
-      <c r="F117" t="s">
-        <v>16</v>
       </c>
       <c r="G117" s="2">
         <v>665773</v>
@@ -3990,22 +3990,22 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B118" s="1">
         <v>46022</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F118" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G118" s="2">
         <v>613085</v>
@@ -4019,22 +4019,22 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B119" s="1">
         <v>46022</v>
       </c>
       <c r="C119" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G119" s="2">
         <v>893683</v>
@@ -4048,22 +4048,22 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B120" s="1">
         <v>46022</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F120" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G120" s="2">
         <v>679300</v>
@@ -4077,22 +4077,22 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B121" s="1">
         <v>46022</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121" t="s">
         <v>24</v>
-      </c>
-      <c r="F121" t="s">
-        <v>25</v>
       </c>
       <c r="G121" s="2">
         <v>839100</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B122" s="1">
         <v>46022</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F122" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G122" s="2">
         <v>2898634.8</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B123" s="1">
         <v>46022</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G123" s="2">
         <v>2140106</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" s="1">
         <v>46022</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E124" t="s">
+        <v>34</v>
+      </c>
+      <c r="F124" t="s">
         <v>35</v>
-      </c>
-      <c r="F124" t="s">
-        <v>36</v>
       </c>
       <c r="G124" s="2">
         <v>2217140</v>
@@ -4193,22 +4193,22 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B125" s="1">
         <v>46022</v>
       </c>
       <c r="C125" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E125" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F125" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G125" s="2">
         <v>895186</v>
@@ -4222,22 +4222,22 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B126" s="1">
         <v>46022</v>
       </c>
       <c r="C126" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G126" s="2">
         <v>757810</v>
@@ -4251,22 +4251,22 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B127" s="1">
         <v>46022</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G127" s="2">
         <v>964300</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B128" s="1">
         <v>46022</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G128" s="2">
         <v>759532</v>
@@ -4309,22 +4309,22 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B129" s="1">
         <v>46022</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" t="s">
         <v>12</v>
-      </c>
-      <c r="F129" t="s">
-        <v>13</v>
       </c>
       <c r="G129" s="2">
         <v>853886</v>
@@ -4338,22 +4338,22 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B130" s="4">
         <v>45930</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G130" s="2">
         <v>1749041.8550000004</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B131" s="4">
         <v>45930</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G131" s="2">
         <v>641625.60000000009</v>
@@ -4396,22 +4396,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B132" s="4">
         <v>45930</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F132" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G132" s="2">
         <v>81867.873999999996</v>
@@ -4425,22 +4425,22 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133" s="4">
         <v>45930</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E133" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" t="s">
         <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>16</v>
       </c>
       <c r="G133" s="2">
         <v>0</v>
@@ -4454,22 +4454,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B134" s="4">
         <v>45930</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G134" s="2">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B135" s="4">
         <v>45930</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G135" s="2">
         <v>0</v>
@@ -4512,22 +4512,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B136" s="4">
         <v>45930</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E136" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F136" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G136" s="2">
         <v>135441.81200000001</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B137" s="4">
         <v>45930</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E137" t="s">
+        <v>23</v>
+      </c>
+      <c r="F137" t="s">
         <v>24</v>
-      </c>
-      <c r="F137" t="s">
-        <v>25</v>
       </c>
       <c r="G137" s="2">
         <v>110000</v>
@@ -4570,22 +4570,22 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B138" s="4">
         <v>45930</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F138" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G138" s="2">
         <v>4399528.18</v>
@@ -4599,22 +4599,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B139" s="4">
         <v>45930</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F139" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G139" s="2">
         <v>681191.12600000005</v>
@@ -4628,22 +4628,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B140" s="4">
         <v>45930</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E140" t="s">
+        <v>34</v>
+      </c>
+      <c r="F140" t="s">
         <v>35</v>
-      </c>
-      <c r="F140" t="s">
-        <v>36</v>
       </c>
       <c r="G140" s="2">
         <v>2068075.97</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B141" s="4">
         <v>45930</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G141" s="2">
         <v>870005.04800000018</v>
@@ -4686,22 +4686,22 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B142" s="4">
         <v>45930</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G142" s="2">
         <v>0</v>
@@ -4715,22 +4715,22 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143" s="4">
         <v>45930</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F143" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G143" s="2">
         <v>360364.13600000006</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B144" s="4">
         <v>45930</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F144" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G144" s="2">
         <v>200000</v>
@@ -4773,22 +4773,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B145" s="4">
         <v>45930</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E145" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" t="s">
         <v>12</v>
-      </c>
-      <c r="F145" t="s">
-        <v>13</v>
       </c>
       <c r="G145" s="2">
         <v>492920.20800000004</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B146" s="4">
         <v>45930</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E146" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F146" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G146" s="2">
         <v>65976823.572000004</v>
@@ -4831,22 +4831,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B147" s="4">
         <v>45961</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G147" s="2">
         <v>2323636.9640000006</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B148" s="4">
         <v>45961</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G148" s="2">
         <v>169330.48</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B149" s="4">
         <v>45961</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G149" s="2">
         <v>11000</v>
@@ -4918,22 +4918,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B150" s="4">
         <v>45961</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E150" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" t="s">
         <v>15</v>
-      </c>
-      <c r="F150" t="s">
-        <v>16</v>
       </c>
       <c r="G150" s="2">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B151" s="4">
         <v>45961</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F151" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G151" s="2">
         <v>0</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B152" s="4">
         <v>45961</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E152" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G152" s="2">
         <v>382649.77300000004</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B153" s="4">
         <v>45961</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E153" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F153" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G153" s="2">
         <v>297697.40000000002</v>
@@ -5034,22 +5034,22 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B154" s="4">
         <v>45961</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E154" t="s">
+        <v>23</v>
+      </c>
+      <c r="F154" t="s">
         <v>24</v>
-      </c>
-      <c r="F154" t="s">
-        <v>25</v>
       </c>
       <c r="G154" s="2">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B155" s="4">
         <v>45961</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E155" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G155" s="2">
         <v>1200000</v>
@@ -5092,22 +5092,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B156" s="4">
         <v>45961</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E156" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G156" s="2">
         <v>1488341.3160000001</v>
@@ -5121,22 +5121,22 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B157" s="4">
         <v>45961</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E157" t="s">
+        <v>34</v>
+      </c>
+      <c r="F157" t="s">
         <v>35</v>
-      </c>
-      <c r="F157" t="s">
-        <v>36</v>
       </c>
       <c r="G157" s="2">
         <v>2808628.79</v>
@@ -5150,22 +5150,22 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B158" s="4">
         <v>45961</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F158" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G158" s="2">
         <v>676632.69300000009</v>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B159" s="4">
         <v>45961</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G159" s="2">
         <v>0</v>
@@ -5208,22 +5208,22 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B160" s="4">
         <v>45961</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F160" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G160" s="2">
         <v>0</v>
@@ -5237,22 +5237,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B161" s="4">
         <v>45961</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F161" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G161" s="2">
         <v>466141.24700000003</v>
@@ -5266,22 +5266,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B162" s="4">
         <v>45961</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E162" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" t="s">
         <v>12</v>
-      </c>
-      <c r="F162" t="s">
-        <v>13</v>
       </c>
       <c r="G162" s="2">
         <v>224274.54500000004</v>
@@ -5295,22 +5295,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B163" s="4">
         <v>45961</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E163" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F163" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G163" s="2">
         <v>63000000</v>
@@ -5324,22 +5324,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B164" s="4">
         <v>45991</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F164" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G164" s="2">
         <v>2617118.1300000004</v>
@@ -5353,22 +5353,22 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B165" s="4">
         <v>45991</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G165" s="2">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B166" s="4">
         <v>45991</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G166" s="2">
         <v>0</v>
@@ -5411,22 +5411,22 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B167" s="4">
         <v>45991</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E167" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167" t="s">
         <v>15</v>
-      </c>
-      <c r="F167" t="s">
-        <v>16</v>
       </c>
       <c r="G167" s="2">
         <v>242414.50200000004</v>
@@ -5440,22 +5440,22 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B168" s="4">
         <v>45991</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G168" s="2">
         <v>237393.64</v>
@@ -5469,22 +5469,22 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B169" s="4">
         <v>45991</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G169" s="2">
         <v>0</v>
@@ -5498,22 +5498,22 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B170" s="4">
         <v>45991</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F170" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G170" s="2">
         <v>590324.35000000009</v>
@@ -5527,22 +5527,22 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B171" s="4">
         <v>45991</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E171" t="s">
+        <v>23</v>
+      </c>
+      <c r="F171" t="s">
         <v>24</v>
-      </c>
-      <c r="F171" t="s">
-        <v>25</v>
       </c>
       <c r="G171" s="2">
         <v>0</v>
@@ -5556,22 +5556,22 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B172" s="4">
         <v>45991</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E172" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F172" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G172" s="2">
         <v>1200000</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B173" s="4">
         <v>45991</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E173" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F173" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G173" s="2">
         <v>2503567.0440000002</v>
@@ -5614,22 +5614,22 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B174" s="4">
         <v>45991</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E174" t="s">
+        <v>34</v>
+      </c>
+      <c r="F174" t="s">
         <v>35</v>
-      </c>
-      <c r="F174" t="s">
-        <v>36</v>
       </c>
       <c r="G174" s="2">
         <v>2313592.94</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B175" s="4">
         <v>45991</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G175" s="2">
         <v>511500.11000000004</v>
@@ -5672,22 +5672,22 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B176" s="4">
         <v>45991</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F176" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G176" s="2">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B177" s="4">
         <v>45991</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E177" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F177" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G177" s="2">
         <v>167752.01300000001</v>
@@ -5730,22 +5730,22 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B178" s="4">
         <v>45991</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F178" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G178" s="2">
         <v>88000</v>
@@ -5759,22 +5759,22 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B179" s="4">
         <v>45991</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E179" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" t="s">
         <v>12</v>
-      </c>
-      <c r="F179" t="s">
-        <v>13</v>
       </c>
       <c r="G179" s="2">
         <v>637238.29400000011</v>
@@ -5788,22 +5788,22 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B180" s="4">
         <v>45991</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E180" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F180" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G180" s="2">
         <v>73000000</v>
@@ -5817,22 +5817,22 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B181" s="4">
         <v>46022</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E181" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F181" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G181" s="2">
         <v>3573244.3670000006</v>
@@ -5846,22 +5846,22 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B182" s="4">
         <v>46022</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F182" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G182" s="2">
         <v>717988.30400000012</v>
@@ -5875,22 +5875,22 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B183" s="4">
         <v>46022</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E183" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F183" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G183" s="2">
         <v>0</v>
@@ -5904,22 +5904,22 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B184" s="4">
         <v>46022</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E184" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" t="s">
         <v>15</v>
-      </c>
-      <c r="F184" t="s">
-        <v>16</v>
       </c>
       <c r="G184" s="2">
         <v>248343.74400000004</v>
@@ -5933,22 +5933,22 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B185" s="4">
         <v>46022</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E185" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G185" s="2">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B186" s="4">
         <v>46022</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E186" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G186" s="2">
         <v>147323</v>
@@ -5991,22 +5991,22 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B187" s="4">
         <v>46022</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F187" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G187" s="2">
         <v>573967.17400000012</v>
@@ -6020,22 +6020,22 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B188" s="4">
         <v>46022</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F188" t="s">
         <v>24</v>
-      </c>
-      <c r="F188" t="s">
-        <v>25</v>
       </c>
       <c r="G188" s="2">
         <v>101021.18400000001</v>
@@ -6049,22 +6049,22 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B189" s="4">
         <v>46022</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E189" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F189" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G189" s="2">
         <v>1200000</v>
@@ -6078,22 +6078,22 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B190" s="4">
         <v>46022</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F190" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G190" s="2">
         <v>3410699.8860000004</v>
@@ -6107,22 +6107,22 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B191" s="4">
         <v>46022</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E191" t="s">
+        <v>34</v>
+      </c>
+      <c r="F191" t="s">
         <v>35</v>
-      </c>
-      <c r="F191" t="s">
-        <v>36</v>
       </c>
       <c r="G191" s="2">
         <v>1978870.38</v>
@@ -6136,22 +6136,22 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B192" s="4">
         <v>46022</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E192" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G192" s="2">
         <v>1165589.5020000001</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B193" s="4">
         <v>46022</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G193" s="2">
         <v>324802.11</v>
@@ -6194,22 +6194,22 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B194" s="4">
         <v>46022</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E194" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F194" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G194" s="2">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B195" s="4">
         <v>46022</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F195" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G195" s="2">
         <v>1373012.3550000002</v>
@@ -6252,22 +6252,22 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B196" s="4">
         <v>46022</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E196" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" t="s">
         <v>12</v>
-      </c>
-      <c r="F196" t="s">
-        <v>13</v>
       </c>
       <c r="G196" s="2">
         <v>1203814.051</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B197" s="4">
         <v>46022</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E197" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F197" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G197" s="2">
         <v>151000000</v>
@@ -6310,22 +6310,22 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B198" s="4">
         <v>45930</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F198" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G198" s="2">
         <v>5397467.5</v>
@@ -6339,22 +6339,22 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B199" s="4">
         <v>45930</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E199" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F199" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G199" s="2">
         <v>829149.99999999988</v>
@@ -6368,22 +6368,22 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B200" s="4">
         <v>45930</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E200" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G200" s="2">
         <v>994802.39999999991</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B201" s="4">
         <v>45930</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E201" t="s">
+        <v>14</v>
+      </c>
+      <c r="F201" t="s">
         <v>15</v>
-      </c>
-      <c r="F201" t="s">
-        <v>16</v>
       </c>
       <c r="G201" s="2">
         <v>459999.99999999994</v>
@@ -6426,22 +6426,22 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B202" s="4">
         <v>45930</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F202" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G202" s="2">
         <v>440728.2</v>
@@ -6455,22 +6455,22 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B203" s="4">
         <v>45930</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F203" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G203" s="2">
         <v>1356850</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B204" s="4">
         <v>45930</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F204" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G204" s="2">
         <v>1096123.6499999999</v>
@@ -6513,22 +6513,22 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B205" s="4">
         <v>45930</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E205" t="s">
+        <v>23</v>
+      </c>
+      <c r="F205" t="s">
         <v>24</v>
-      </c>
-      <c r="F205" t="s">
-        <v>25</v>
       </c>
       <c r="G205" s="2">
         <v>399880</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B206" s="4">
         <v>45930</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E206" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F206" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G206" s="2">
         <v>6377053</v>
@@ -6571,22 +6571,22 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B207" s="4">
         <v>45930</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F207" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G207" s="2">
         <v>4547275</v>
@@ -6600,22 +6600,22 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B208" s="4">
         <v>45930</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E208" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" t="s">
         <v>35</v>
-      </c>
-      <c r="F208" t="s">
-        <v>36</v>
       </c>
       <c r="G208" s="2">
         <v>2852201</v>
@@ -6629,22 +6629,22 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B209" s="4">
         <v>45930</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F209" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G209" s="2">
         <v>2909552.1</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B210" s="4">
         <v>45930</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G210" s="2">
         <v>1252002</v>
@@ -6687,22 +6687,22 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B211" s="4">
         <v>45930</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E211" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F211" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G211" s="2">
         <v>1225665</v>
@@ -6716,22 +6716,22 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B212" s="4">
         <v>45930</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F212" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G212" s="2">
         <v>1631437.5</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B213" s="4">
         <v>45930</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E213" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" t="s">
         <v>12</v>
-      </c>
-      <c r="F213" t="s">
-        <v>13</v>
       </c>
       <c r="G213" s="2">
         <v>719750</v>
@@ -6774,22 +6774,22 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B214" s="4">
         <v>45961</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E214" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G214" s="2">
         <v>3102586.15</v>
@@ -6803,22 +6803,22 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B215" s="4">
         <v>45961</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F215" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G215" s="2">
         <v>508299.99999999994</v>
@@ -6832,22 +6832,22 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B216" s="4">
         <v>45961</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E216" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F216" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G216" s="2">
         <v>573000</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B217" s="4">
         <v>45961</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E217" t="s">
+        <v>14</v>
+      </c>
+      <c r="F217" t="s">
         <v>15</v>
-      </c>
-      <c r="F217" t="s">
-        <v>16</v>
       </c>
       <c r="G217" s="2">
         <v>403649.99999999994</v>
@@ -6890,22 +6890,22 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B218" s="4">
         <v>45961</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E218" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F218" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G218" s="2">
         <v>669570</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B219" s="4">
         <v>45961</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F219" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G219" s="2">
         <v>1252131.1000000001</v>
@@ -6948,22 +6948,22 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B220" s="4">
         <v>45961</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F220" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G220" s="2">
         <v>1163801.1499999999</v>
@@ -6977,22 +6977,22 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B221" s="4">
         <v>45961</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E221" t="s">
+        <v>23</v>
+      </c>
+      <c r="F221" t="s">
         <v>24</v>
-      </c>
-      <c r="F221" t="s">
-        <v>25</v>
       </c>
       <c r="G221" s="2">
         <v>232570</v>
@@ -7006,22 +7006,22 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B222" s="4">
         <v>45961</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E222" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F222" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G222" s="2">
         <v>6000000</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B223" s="4">
         <v>45961</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E223" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F223" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G223" s="2">
         <v>3775394</v>
@@ -7064,22 +7064,22 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B224" s="4">
         <v>45961</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E224" t="s">
+        <v>34</v>
+      </c>
+      <c r="F224" t="s">
         <v>35</v>
-      </c>
-      <c r="F224" t="s">
-        <v>36</v>
       </c>
       <c r="G224" s="2">
         <v>3961647</v>
@@ -7093,22 +7093,22 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B225" s="4">
         <v>45961</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E225" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F225" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G225" s="2">
         <v>910772.10000000009</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B226" s="4">
         <v>45961</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E226" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F226" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G226" s="2">
         <v>291637</v>
@@ -7151,22 +7151,22 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B227" s="4">
         <v>45961</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E227" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F227" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G227" s="2">
         <v>1278900</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B228" s="4">
         <v>45961</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E228" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F228" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G228" s="2">
         <v>570151.05000000005</v>
@@ -7209,22 +7209,22 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B229" s="4">
         <v>45961</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E229" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" t="s">
         <v>12</v>
-      </c>
-      <c r="F229" t="s">
-        <v>13</v>
       </c>
       <c r="G229" s="2">
         <v>971855</v>
@@ -7238,22 +7238,22 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B230" s="4">
         <v>45991</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E230" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F230" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G230" s="2">
         <v>3654587.76</v>
@@ -7267,22 +7267,22 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B231" s="4">
         <v>45991</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E231" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F231" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G231" s="2">
         <v>1237278.0999999999</v>
@@ -7296,22 +7296,22 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B232" s="4">
         <v>45991</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E232" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F232" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G232" s="2">
         <v>807933.6</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B233" s="4">
         <v>45991</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E233" t="s">
+        <v>14</v>
+      </c>
+      <c r="F233" t="s">
         <v>15</v>
-      </c>
-      <c r="F233" t="s">
-        <v>16</v>
       </c>
       <c r="G233" s="2">
         <v>259899.99999999997</v>
@@ -7354,22 +7354,22 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B234" s="4">
         <v>45991</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E234" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F234" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G234" s="2">
         <v>657454.57799999998</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B235" s="4">
         <v>45991</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F235" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G235" s="2">
         <v>1578659.5000000002</v>
@@ -7412,22 +7412,22 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B236" s="4">
         <v>45991</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F236" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G236" s="2">
         <v>2057696.15</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B237" s="4">
         <v>45991</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E237" t="s">
+        <v>23</v>
+      </c>
+      <c r="F237" t="s">
         <v>24</v>
-      </c>
-      <c r="F237" t="s">
-        <v>25</v>
       </c>
       <c r="G237" s="2">
         <v>838240</v>
@@ -7470,22 +7470,22 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B238" s="4">
         <v>45991</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F238" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G238" s="2">
         <v>5000000</v>
@@ -7499,22 +7499,22 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B239" s="4">
         <v>45991</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E239" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F239" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G239" s="2">
         <v>5277678</v>
@@ -7528,22 +7528,22 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B240" s="4">
         <v>45991</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E240" t="s">
+        <v>34</v>
+      </c>
+      <c r="F240" t="s">
         <v>35</v>
-      </c>
-      <c r="F240" t="s">
-        <v>36</v>
       </c>
       <c r="G240" s="2">
         <v>6257204</v>
@@ -7557,22 +7557,22 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B241" s="4">
         <v>45991</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E241" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F241" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G241" s="2">
         <v>859425</v>
@@ -7586,22 +7586,22 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B242" s="4">
         <v>45991</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E242" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F242" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G242" s="2">
         <v>1321101</v>
@@ -7615,22 +7615,22 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B243" s="4">
         <v>45991</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E243" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F243" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G243" s="2">
         <v>2055585</v>
@@ -7644,22 +7644,22 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B244" s="4">
         <v>45991</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F244" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G244" s="2">
         <v>1198640.1000000001</v>
@@ -7673,22 +7673,22 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B245" s="4">
         <v>45991</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E245" t="s">
+        <v>11</v>
+      </c>
+      <c r="F245" t="s">
         <v>12</v>
-      </c>
-      <c r="F245" t="s">
-        <v>13</v>
       </c>
       <c r="G245" s="2">
         <v>905600</v>
@@ -7702,22 +7702,22 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B246" s="4">
         <v>46022</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E246" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F246" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G246" s="2">
         <v>4831669.8</v>
@@ -7731,22 +7731,22 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B247" s="4">
         <v>46022</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E247" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F247" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G247" s="2">
         <v>681950</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B248" s="4">
         <v>46022</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E248" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F248" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G248" s="2">
         <v>756000</v>
@@ -7789,22 +7789,22 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B249" s="4">
         <v>46022</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E249" t="s">
+        <v>14</v>
+      </c>
+      <c r="F249" t="s">
         <v>15</v>
-      </c>
-      <c r="F249" t="s">
-        <v>16</v>
       </c>
       <c r="G249" s="2">
         <v>0</v>
@@ -7818,22 +7818,22 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B250" s="4">
         <v>46022</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F250" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G250" s="2">
         <v>165000</v>
@@ -7847,22 +7847,22 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B251" s="4">
         <v>46022</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F251" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G251" s="2">
         <v>466400.00000000006</v>
@@ -7876,22 +7876,22 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B252" s="4">
         <v>46022</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F252" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G252" s="2">
         <v>2223583.65</v>
@@ -7905,22 +7905,22 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B253" s="4">
         <v>46022</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E253" t="s">
+        <v>23</v>
+      </c>
+      <c r="F253" t="s">
         <v>24</v>
-      </c>
-      <c r="F253" t="s">
-        <v>25</v>
       </c>
       <c r="G253" s="2">
         <v>361300</v>
@@ -7934,22 +7934,22 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B254" s="4">
         <v>46022</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E254" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F254" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G254" s="2">
         <v>7000000</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B255" s="4">
         <v>46022</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E255" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F255" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G255" s="2">
         <v>5874671</v>
@@ -7992,22 +7992,22 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B256" s="4">
         <v>46022</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E256" t="s">
+        <v>34</v>
+      </c>
+      <c r="F256" t="s">
         <v>35</v>
-      </c>
-      <c r="F256" t="s">
-        <v>36</v>
       </c>
       <c r="G256" s="2">
         <v>6213700</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B257" s="4">
         <v>46022</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E257" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F257" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G257" s="2">
         <v>851551.05</v>
@@ -8050,22 +8050,22 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B258" s="4">
         <v>46022</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E258" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F258" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G258" s="2">
         <v>1073698</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B259" s="4">
         <v>46022</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E259" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F259" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G259" s="2">
         <v>1281033.6000000001</v>
@@ -8108,22 +8108,22 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B260" s="4">
         <v>46022</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E260" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F260" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G260" s="2">
         <v>1345051.05</v>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B261" s="4">
         <v>46022</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E261" t="s">
+        <v>11</v>
+      </c>
+      <c r="F261" t="s">
         <v>12</v>
-      </c>
-      <c r="F261" t="s">
-        <v>13</v>
       </c>
       <c r="G261" s="2">
         <v>1845067.55</v>
@@ -8166,22 +8166,22 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B262" s="1">
         <v>45930</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E262" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F262" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G262" s="2">
         <v>64000.000000000015</v>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B263" s="1">
         <v>45930</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E263" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F263" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G263" s="2">
         <v>64000.000000000015</v>
@@ -8224,22 +8224,22 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B264" s="1">
         <v>45930</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E264" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F264" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G264" s="2">
         <v>64000.000000000015</v>
@@ -8253,22 +8253,22 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B265" s="1">
         <v>45930</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E265" t="s">
+        <v>14</v>
+      </c>
+      <c r="F265" t="s">
         <v>15</v>
-      </c>
-      <c r="F265" t="s">
-        <v>16</v>
       </c>
       <c r="G265" s="2">
         <v>64000.000000000015</v>
@@ -8282,22 +8282,22 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B266" s="1">
         <v>45930</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E266" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F266" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G266" s="2">
         <v>64000.000000000015</v>
@@ -8311,22 +8311,22 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B267" s="1">
         <v>45930</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E267" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F267" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G267" s="2">
         <v>64000.000000000015</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B268" s="1">
         <v>45930</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E268" t="s">
+        <v>23</v>
+      </c>
+      <c r="F268" t="s">
         <v>24</v>
-      </c>
-      <c r="F268" t="s">
-        <v>25</v>
       </c>
       <c r="G268" s="2">
         <v>64000.000000000015</v>
@@ -8369,22 +8369,22 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B269" s="1">
         <v>45930</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E269" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F269" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G269" s="2">
         <v>64000.000000000015</v>
@@ -8398,22 +8398,22 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B270" s="1">
         <v>45930</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E270" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F270" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G270" s="2">
         <v>64000.000000000015</v>
@@ -8427,22 +8427,22 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B271" s="1">
         <v>45930</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E271" t="s">
+        <v>34</v>
+      </c>
+      <c r="F271" t="s">
         <v>35</v>
-      </c>
-      <c r="F271" t="s">
-        <v>36</v>
       </c>
       <c r="G271" s="2">
         <v>64000.000000000015</v>
@@ -8456,22 +8456,22 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B272" s="1">
         <v>45930</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E272" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F272" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G272" s="2">
         <v>64000.000000000015</v>
@@ -8485,22 +8485,22 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B273" s="1">
         <v>45930</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E273" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F273" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G273" s="2">
         <v>64000.000000000015</v>
@@ -8514,22 +8514,22 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B274" s="1">
         <v>45930</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F274" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G274" s="2">
         <v>64000.000000000015</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B275" s="1">
         <v>45930</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E275" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F275" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G275" s="2">
         <v>64000.000000000015</v>
@@ -8572,22 +8572,22 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B276" s="1">
         <v>45930</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E276" t="s">
+        <v>11</v>
+      </c>
+      <c r="F276" t="s">
         <v>12</v>
-      </c>
-      <c r="F276" t="s">
-        <v>13</v>
       </c>
       <c r="G276" s="2">
         <v>64000.000000000015</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B277" s="1">
         <v>45930</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E277" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F277" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G277" s="2">
         <v>320000.00000000006</v>
@@ -8630,22 +8630,22 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B278" s="1">
         <v>45961</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E278" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F278" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G278" s="2">
         <v>64000.000000000015</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B279" s="1">
         <v>45961</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E279" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F279" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G279" s="2">
         <v>64000.000000000015</v>
@@ -8688,22 +8688,22 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B280" s="1">
         <v>45961</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F280" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G280" s="2">
         <v>64000.000000000015</v>
@@ -8717,22 +8717,22 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B281" s="1">
         <v>45961</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E281" t="s">
+        <v>14</v>
+      </c>
+      <c r="F281" t="s">
         <v>15</v>
-      </c>
-      <c r="F281" t="s">
-        <v>16</v>
       </c>
       <c r="G281" s="2">
         <v>64000.000000000015</v>
@@ -8746,22 +8746,22 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B282" s="1">
         <v>45961</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E282" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F282" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G282" s="2">
         <v>64000.000000000015</v>
@@ -8775,22 +8775,22 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B283" s="1">
         <v>45961</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E283" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F283" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G283" s="2">
         <v>64000.000000000015</v>
@@ -8804,22 +8804,22 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B284" s="1">
         <v>45961</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E284" t="s">
+        <v>23</v>
+      </c>
+      <c r="F284" t="s">
         <v>24</v>
-      </c>
-      <c r="F284" t="s">
-        <v>25</v>
       </c>
       <c r="G284" s="2">
         <v>64000.000000000015</v>
@@ -8833,22 +8833,22 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B285" s="1">
         <v>45961</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E285" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F285" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G285" s="2">
         <v>64000.000000000015</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B286" s="1">
         <v>45961</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E286" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F286" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G286" s="2">
         <v>64000.000000000015</v>
@@ -8891,22 +8891,22 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B287" s="1">
         <v>45961</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E287" t="s">
+        <v>34</v>
+      </c>
+      <c r="F287" t="s">
         <v>35</v>
-      </c>
-      <c r="F287" t="s">
-        <v>36</v>
       </c>
       <c r="G287" s="2">
         <v>64000.000000000015</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B288" s="1">
         <v>45961</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E288" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G288" s="2">
         <v>64000.000000000015</v>
@@ -8949,22 +8949,22 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B289" s="1">
         <v>45961</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E289" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G289" s="2">
         <v>64000.000000000015</v>
@@ -8978,22 +8978,22 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B290" s="1">
         <v>45961</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E290" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F290" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G290" s="2">
         <v>64000.000000000015</v>
@@ -9007,22 +9007,22 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B291" s="1">
         <v>45961</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E291" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F291" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G291" s="2">
         <v>64000.000000000015</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B292" s="1">
         <v>45961</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E292" t="s">
+        <v>11</v>
+      </c>
+      <c r="F292" t="s">
         <v>12</v>
-      </c>
-      <c r="F292" t="s">
-        <v>13</v>
       </c>
       <c r="G292" s="2">
         <v>64000.000000000015</v>
@@ -9065,22 +9065,22 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B293" s="1">
         <v>45961</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E293" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F293" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G293" s="2">
         <v>320000.00000000006</v>
@@ -9094,22 +9094,22 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B294" s="1">
         <v>45991</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G294" s="2">
         <v>64000.000000000015</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B295" s="1">
         <v>45991</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E295" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F295" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G295" s="2">
         <v>64000.000000000015</v>
@@ -9152,22 +9152,22 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B296" s="1">
         <v>45991</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E296" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F296" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G296" s="2">
         <v>64000.000000000015</v>
@@ -9181,22 +9181,22 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B297" s="1">
         <v>45991</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E297" t="s">
+        <v>14</v>
+      </c>
+      <c r="F297" t="s">
         <v>15</v>
-      </c>
-      <c r="F297" t="s">
-        <v>16</v>
       </c>
       <c r="G297" s="2">
         <v>64000.000000000015</v>
@@ -9210,22 +9210,22 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B298" s="1">
         <v>45991</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E298" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F298" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G298" s="2">
         <v>64000.000000000015</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B299" s="1">
         <v>45991</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E299" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F299" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G299" s="2">
         <v>64000.000000000015</v>
@@ -9268,22 +9268,22 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B300" s="1">
         <v>45991</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E300" t="s">
+        <v>23</v>
+      </c>
+      <c r="F300" t="s">
         <v>24</v>
-      </c>
-      <c r="F300" t="s">
-        <v>25</v>
       </c>
       <c r="G300" s="2">
         <v>64000.000000000015</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B301" s="1">
         <v>45991</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E301" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F301" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G301" s="2">
         <v>64000.000000000015</v>
@@ -9326,22 +9326,22 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B302" s="1">
         <v>45991</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E302" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F302" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G302" s="2">
         <v>64000.000000000015</v>
@@ -9355,22 +9355,22 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B303" s="1">
         <v>45991</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E303" t="s">
+        <v>34</v>
+      </c>
+      <c r="F303" t="s">
         <v>35</v>
-      </c>
-      <c r="F303" t="s">
-        <v>36</v>
       </c>
       <c r="G303" s="2">
         <v>64000.000000000015</v>
@@ -9384,22 +9384,22 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B304" s="1">
         <v>45991</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E304" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F304" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G304" s="2">
         <v>64000.000000000015</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B305" s="1">
         <v>45991</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E305" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F305" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G305" s="2">
         <v>64000.000000000015</v>
@@ -9442,22 +9442,22 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B306" s="1">
         <v>45991</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E306" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F306" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G306" s="2">
         <v>64000.000000000015</v>
@@ -9471,22 +9471,22 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B307" s="1">
         <v>45991</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E307" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F307" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G307" s="2">
         <v>64000.000000000015</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B308" s="1">
         <v>45991</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E308" t="s">
+        <v>11</v>
+      </c>
+      <c r="F308" t="s">
         <v>12</v>
-      </c>
-      <c r="F308" t="s">
-        <v>13</v>
       </c>
       <c r="G308" s="2">
         <v>64000.000000000015</v>
@@ -9529,22 +9529,22 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B309" s="1">
         <v>45991</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E309" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F309" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G309" s="2">
         <v>320000.00000000006</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B310" s="1">
         <v>46022</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F310" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G310" s="2">
         <v>64000.000000000015</v>
@@ -9587,22 +9587,22 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B311" s="1">
         <v>46022</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E311" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F311" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G311" s="2">
         <v>64000.000000000015</v>
@@ -9616,22 +9616,22 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B312" s="1">
         <v>46022</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F312" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G312" s="2">
         <v>64000.000000000015</v>
@@ -9645,22 +9645,22 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B313" s="1">
         <v>46022</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E313" t="s">
+        <v>14</v>
+      </c>
+      <c r="F313" t="s">
         <v>15</v>
-      </c>
-      <c r="F313" t="s">
-        <v>16</v>
       </c>
       <c r="G313" s="2">
         <v>64000.000000000015</v>
@@ -9674,22 +9674,22 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B314" s="1">
         <v>46022</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F314" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G314" s="2">
         <v>64000.000000000015</v>
@@ -9703,22 +9703,22 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B315" s="1">
         <v>46022</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E315" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F315" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G315" s="2">
         <v>64000.000000000015</v>
@@ -9732,22 +9732,22 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B316" s="1">
         <v>46022</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E316" t="s">
+        <v>23</v>
+      </c>
+      <c r="F316" t="s">
         <v>24</v>
-      </c>
-      <c r="F316" t="s">
-        <v>25</v>
       </c>
       <c r="G316" s="2">
         <v>64000.000000000015</v>
@@ -9761,22 +9761,22 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B317" s="1">
         <v>46022</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E317" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F317" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G317" s="2">
         <v>64000.000000000015</v>
@@ -9790,22 +9790,22 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B318" s="1">
         <v>46022</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E318" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F318" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G318" s="2">
         <v>64000.000000000015</v>
@@ -9819,22 +9819,22 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B319" s="1">
         <v>46022</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E319" t="s">
+        <v>34</v>
+      </c>
+      <c r="F319" t="s">
         <v>35</v>
-      </c>
-      <c r="F319" t="s">
-        <v>36</v>
       </c>
       <c r="G319" s="2">
         <v>64000.000000000015</v>
@@ -9848,22 +9848,22 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B320" s="1">
         <v>46022</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E320" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F320" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G320" s="2">
         <v>64000.000000000015</v>
@@ -9877,22 +9877,22 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B321" s="1">
         <v>46022</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E321" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F321" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G321" s="2">
         <v>64000.000000000015</v>
@@ -9906,22 +9906,22 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B322" s="1">
         <v>46022</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E322" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F322" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G322" s="2">
         <v>64000.000000000015</v>
@@ -9935,22 +9935,22 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B323" s="1">
         <v>46022</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E323" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F323" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G323" s="2">
         <v>64000.000000000015</v>
@@ -9964,22 +9964,22 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B324" s="1">
         <v>46022</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E324" t="s">
+        <v>11</v>
+      </c>
+      <c r="F324" t="s">
         <v>12</v>
-      </c>
-      <c r="F324" t="s">
-        <v>13</v>
       </c>
       <c r="G324" s="2">
         <v>64000.000000000015</v>
@@ -9993,22 +9993,22 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B325" s="1">
         <v>46022</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E325" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F325" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G325" s="2">
         <v>320000.00000000006</v>
@@ -10022,22 +10022,22 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B326" s="1">
         <v>45930</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D326" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E326" t="s">
         <v>56</v>
       </c>
-      <c r="E326" t="s">
-        <v>57</v>
-      </c>
       <c r="F326" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G326" s="2">
         <v>35000000</v>
@@ -10051,22 +10051,22 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B327" s="1">
         <v>45961</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D327" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E327" t="s">
         <v>56</v>
       </c>
-      <c r="E327" t="s">
-        <v>57</v>
-      </c>
       <c r="F327" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G327" s="2">
         <v>31000000</v>
@@ -10080,22 +10080,22 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B328" s="1">
         <v>45991</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D328" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E328" t="s">
         <v>56</v>
       </c>
-      <c r="E328" t="s">
-        <v>57</v>
-      </c>
       <c r="F328" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G328" s="2">
         <v>30000000</v>
@@ -10109,22 +10109,22 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B329" s="1">
         <v>46022</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D329" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E329" t="s">
         <v>56</v>
       </c>
-      <c r="E329" t="s">
-        <v>57</v>
-      </c>
       <c r="F329" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G329" s="2">
         <v>35000000</v>

--- a/data/Branch Plan 2025.xlsx
+++ b/data/Branch Plan 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATK_Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C0B97C-4CBF-44CE-84F4-451699341087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51B3E62-B962-4B51-9C91-3C04063048E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="2250" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25635" yWindow="1815" windowWidth="22710" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -210,7 +210,7 @@
     <t>Retail Creditare</t>
   </si>
   <si>
-    <t>Produs_Adjusted</t>
+    <t>Product_Adjusted</t>
   </si>
 </sst>
 </file>
